--- a/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>135 / 361</t>
+          <t>134 / 361</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ID 2.6 m (top) / 6.4 m (main) / 3.0 m (boot) x 36.0 m T/T</t>
+          <t>ID 2.6 m (top) / 6.6 m (main) / 3.0 m (boot) x 36.0 m T/T</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60.8 MW abs. / 67.6 MW fired; 2-cell cabin, 8 passes, 128 rad. tubes 6" x 18.3 m</t>
+          <t>60.7 MW abs. / 67.4 MW fired; 2-cell cabin, 8 passes, 128 rad. tubes 6" x 18.3 m</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -987,7 +987,7 @@
         <v>3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>60.81</v>
+        <v>60.68</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14.7 MW abs. / 16.8 MW fired; 1-cell cabin, 4 passes, 40 rad. tubes 6" x 18.3 m</t>
+          <t>14.7 MW abs. / 16.7 MW fired; 1-cell cabin, 4 passes, 40 rad. tubes 6" x 18.3 m</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>14.74</v>
+        <v>14.69</v>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357 m2 total; 1S x 1P shells</t>
+          <t>359 m2 total; 1S x 1P shells</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
@@ -1245,13 +1245,13 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>435 m2 total; 1S x 1P shells</t>
+          <t>438 m2 total; 1S x 1P shells</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>H 210-&gt;76 / C 56-&gt;75</t>
+          <t>H 212-&gt;76 / C 56-&gt;75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
@@ -1300,13 +1300,13 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>811 m2 total; 2S x 1P shells</t>
+          <t>804 m2 total; 2S x 1P shells</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>H 221-&gt;95 / C 75-&gt;108</t>
+          <t>H 224-&gt;95 / C 75-&gt;108</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
         <v>3</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>11.37</v>
+        <v>11.45</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
@@ -1355,13 +1355,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379 m2 total; 1S x 1P shells</t>
+          <t>378 m2 total; 1S x 1P shells</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>H 205-&gt;128 / C 108-&gt;120</t>
+          <t>H 205-&gt;128 / C 108-&gt;121</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         <v>3</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
@@ -1410,13 +1410,13 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>430 m2 total; 1S x 1P shells</t>
+          <t>431 m2 total; 1S x 1P shells</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>H 255-&gt;175 / C 120-&gt;136</t>
+          <t>H 255-&gt;175 / C 121-&gt;136</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1465,13 +1465,13 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1041 m2 total; 2S x 1P shells</t>
+          <t>1001 m2 total; 2S x 1P shells</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>H 238-&gt;158 / C 136-&gt;169</t>
+          <t>H 240-&gt;160 / C 136-&gt;170</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>12.87</v>
+        <v>12.85</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
@@ -1520,13 +1520,13 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318 m2 total; 1S x 1P shells</t>
+          <t>324 m2 total; 1S x 1P shells</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>H 292-&gt;205 / C 169-&gt;184</t>
+          <t>H 294-&gt;205 / C 170-&gt;184</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
         <v>6</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.7</v>
+        <v>5.83</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2155 m2 total; 2S x 2P shells</t>
+          <t>2196 m2 total; 2S x 2P shells</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1603,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>21.21</v>
+        <v>21.14</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
@@ -1658,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
@@ -1685,13 +1685,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>876 m2 total; 1S x 2P shells</t>
+          <t>886 m2 total; 1S x 2P shells</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>H 313-&gt;261 / C 241-&gt;257</t>
+          <t>H 314-&gt;261 / C 241-&gt;258</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.35</v>
+        <v>7.46</v>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
@@ -1740,13 +1740,13 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1098 m2 total; 1S x 2P shells</t>
+          <t>1094 m2 total; 1S x 2P shells</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>H 366-&gt;277 / C 257-&gt;274</t>
+          <t>H 366-&gt;278 / C 258-&gt;274</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
         <v>6</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>7.61</v>
+        <v>7.58</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
@@ -1795,13 +1795,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>233 m2; 1 shell(s)</t>
+          <t>223 m2; 1 shell(s)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>H 261-&gt;223 / C 186-&gt;186</t>
+          <t>H 261-&gt;224 / C 186-&gt;186</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
         <v>3</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>5.04</v>
+        <v>4.91</v>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
@@ -1850,13 +1850,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>645 m2; 1 shell(s)</t>
+          <t>648 m2; 1 shell(s)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>H 277-&gt;175 / C 148-&gt;148</t>
+          <t>H 278-&gt;175 / C 148-&gt;148</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
         <v>3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>7.58</v>
+        <v>7.62</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
@@ -1933,7 +1933,7 @@
         <v>3</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>741 m2; 2 shell(s)</t>
+          <t>740 m2; 2 shell(s)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
         <v>3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
@@ -2043,7 +2043,7 @@
         <v>3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.49</v>
+        <v>8.51</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
@@ -2345,13 +2345,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1658 m2 bare; 2 bay(s) 6 m x 12 m, 4 fans</t>
+          <t>1667 m2 bare; 2 bay(s) 6 m x 12 m, 4 fans</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>135-&gt;60 (air 35-&gt;55)</t>
+          <t>134-&gt;60 (air 35-&gt;55)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="3" t="n">
-        <v>33.81</v>
+        <v>33.75</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>90</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>286 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
+          <t>287 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>6.03</v>
+        <v>6.06</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>30</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>45</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="3" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>30</v>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>404 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
+          <t>397 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>15</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>402 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
+          <t>403 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>load 3021 kg/h, motive MP steam 7855 kg/h (2 x 50 % parallel)</t>
+          <t>load 3020 kg/h, motive MP steam 7852 kg/h (2 x 50 % parallel)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>158 m3/h rated @ 102 m</t>
+          <t>159 m3/h rated @ 102 m</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3788,13 +3788,13 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>388 m3/h rated @ 137 m</t>
+          <t>387 m3/h rated @ 138 m</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3886,13 +3886,13 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>122 m3/h rated @ 147 m</t>
+          <t>122 m3/h rated @ 148 m</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3941,13 +3941,13 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>84 m3/h rated @ 152 m</t>
+          <t>84 m3/h rated @ 153 m</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -4327,19 +4327,19 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>202 m3/h rated @ 138 m</t>
+          <t>198 m3/h rated @ 138 m</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>392 m3/h rated @ 144 m</t>
+          <t>391 m3/h rated @ 144 m</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>805.2</v>
+        <v>805.4</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>263</v>
@@ -4930,7 +4930,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>136.0607976966045</v>
+        <v>136.3520743392695</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>776</v>
@@ -4939,7 +4939,7 @@
         <v>0.73</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>615.7</v>
+        <v>615.9</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>710</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>158.3</v>
+        <v>158.6</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>102</v>
@@ -4990,7 +4990,7 @@
         <v>0.67</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>55</v>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>179.6</v>
+        <v>179.9</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>232</v>
@@ -5041,7 +5041,7 @@
         <v>0.67</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>118.4</v>
+        <v>118.6</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>160</v>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>51</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>293</v>
+        <v>292.6</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>130</v>
@@ -5134,7 +5134,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>153.263408402976</v>
+        <v>152.8292885846183</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>627</v>
@@ -5143,7 +5143,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>94.2</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>110</v>
@@ -5176,25 +5176,25 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>387.9</v>
+        <v>387.4</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>238.4964546011054</v>
+        <v>240.0155698591315</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>122.9</v>
+        <v>122.8</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>160</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>318.3</v>
+        <v>317.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>142</v>
@@ -5236,16 +5236,16 @@
         <v>8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>312.6428096410828</v>
+        <v>313.9004413771325</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>132</v>
@@ -5281,16 +5281,16 @@
         <v>121.5</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>210.0576955067695</v>
+        <v>211.5077376719267</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.66</v>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>150.6</v>
+        <v>151</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>154</v>
@@ -5338,16 +5338,16 @@
         <v>9</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>291.812731884113</v>
+        <v>293.539066420746</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.67</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>56.3</v>
+        <v>56.5</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>75</v>
@@ -5380,25 +5380,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>334.5796577406791</v>
+        <v>334.7436496087009</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>45</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>398.1</v>
+        <v>397.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>172</v>
@@ -5440,7 +5440,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>348.5796577406791</v>
+        <v>348.7436496087009</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>710</v>
@@ -5449,7 +5449,7 @@
         <v>0.7</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>189</v>
+        <v>188.9</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>250</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>146.2</v>
+        <v>146.3</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>111</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>142.1</v>
+        <v>142.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>98</v>
@@ -5644,7 +5644,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>152.3756223899362</v>
+        <v>152.3137756213287</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>624</v>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>201.7</v>
+        <v>198.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>138</v>
@@ -5746,16 +5746,16 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>220.5624132856465</v>
+        <v>223.7069906480531</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>110</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>392.2</v>
+        <v>391</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>144</v>
@@ -5797,16 +5797,16 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>315.1768033292034</v>
+        <v>314.9938703914651</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>155.3</v>
+        <v>154.8</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>200</v>
@@ -5848,7 +5848,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>378.3139675704387</v>
+        <v>378.4357134139163</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>714</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>195.5</v>
+        <v>195.6</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>187</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>366.3139675704387</v>
+        <v>366.4357134139163</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>761</v>
@@ -6126,19 +6126,19 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>215865</v>
+        <v>216219</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>51052</v>
+        <v>51101</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>101893</v>
+        <v>102070</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>13</v>
@@ -6306,7 +6306,7 @@
         <v>54.2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7163</v>
+        <v>7175</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>76886</v>
+        <v>76867</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>3.5</v>
@@ -6390,7 +6390,7 @@
         <v>81</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14023</v>
+        <v>14019</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>32790</v>
+        <v>32789</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>3.5</v>
@@ -6558,7 +6558,7 @@
         <v>60</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9338</v>
+        <v>9337</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -6784,11 +6784,11 @@
         <v>300</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>H 210-&gt;76 / C 56-&gt;75</t>
+          <t>H 212-&gt;76 / C 56-&gt;75</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>11.37</v>
+        <v>11.45</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>H 221-&gt;95 / C 75-&gt;108</t>
+          <t>H 224-&gt;95 / C 75-&gt;108</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>H 205-&gt;128 / C 108-&gt;120</t>
+          <t>H 205-&gt;128 / C 108-&gt;121</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
         <v>5.84</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>H 255-&gt;175 / C 120-&gt;136</t>
+          <t>H 255-&gt;175 / C 121-&gt;136</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>12.87</v>
+        <v>12.85</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1041</v>
+        <v>1001</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2</v>
@@ -6992,11 +6992,11 @@
         <v>320</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>H 238-&gt;158 / C 136-&gt;169</t>
+          <t>H 240-&gt;160 / C 136-&gt;170</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7032,10 +7032,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5.7</v>
+        <v>5.83</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -7044,11 +7044,11 @@
         <v>290</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>H 292-&gt;205 / C 169-&gt;184</t>
+          <t>H 294-&gt;205 / C 170-&gt;184</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21.21</v>
+        <v>21.14</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2155</v>
+        <v>2196</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>4</v>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>263</v>
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7.35</v>
+        <v>7.46</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>876</v>
+        <v>886</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>2</v>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>H 313-&gt;261 / C 241-&gt;257</t>
+          <t>H 314-&gt;261 / C 241-&gt;258</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>7.61</v>
+        <v>7.58</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>2</v>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>H 366-&gt;277 / C 257-&gt;274</t>
+          <t>H 366-&gt;278 / C 258-&gt;274</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7292,10 +7292,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5.04</v>
+        <v>4.91</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -7306,7 +7306,7 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>H 261-&gt;223 / C 186-&gt;186</t>
+          <t>H 261-&gt;224 / C 186-&gt;186</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>7.58</v>
+        <v>7.62</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
@@ -7356,7 +7356,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>H 277-&gt;175 / C 148-&gt;148</t>
+          <t>H 278-&gt;175 / C 148-&gt;148</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>117</v>
@@ -7442,10 +7442,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>2</v>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>8.49</v>
+        <v>8.51</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>190</v>
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>33.81</v>
+        <v>33.75</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2</v>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>135-&gt;60 (air 35-&gt;55)</t>
+          <t>134-&gt;60 (air 35-&gt;55)</t>
         </is>
       </c>
     </row>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6.03</v>
+        <v>6.06</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>881</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>401</v>
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -8112,7 +8112,7 @@
         <v>6.64</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>

--- a/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ID 6.9 m (top/main) / 4.1 m (stripping) x 40.5 m T/T</t>
+          <t>ID 6.9 m (top/main) / 4.1 m (stripping) x 36.0 m T/T</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">

--- a/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
@@ -1850,13 +1850,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>648 m2; 1 shell(s)</t>
+          <t>84 m2; 1 shell(s)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>H 278-&gt;175 / C 148-&gt;148</t>
+          <t>H 278-&gt;255 / C 148-&gt;148</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
         <v>3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>7.62</v>
+        <v>1.78</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
@@ -1905,13 +1905,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>117 m2; 1 shell(s)</t>
+          <t>86 m2; 1 shell(s)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>H 203-&gt;163 / C 77-&gt;120</t>
+          <t>H 203-&gt;163 / C 45-&gt;91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>190 m2; 1 shell(s)</t>
+          <t>242 m2; 1 shell(s)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
         <v>3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8.51</v>
+        <v>10.83</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
@@ -2455,13 +2455,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>430 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
+          <t>302 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>205-&gt;55 (air 35-&gt;50)</t>
+          <t>128-&gt;55 (air 35-&gt;50)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2481,10 +2481,10 @@
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="3" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>45</v>
+        <v>3.72</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>18.5</v>
       </c>
     </row>
     <row r="38">
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>102070</v>
+        <v>129912</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>13</v>
@@ -6306,7 +6306,7 @@
         <v>54.2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7175</v>
+        <v>9132</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>7.62</v>
+        <v>1.78</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>648</v>
+        <v>84</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
@@ -7356,7 +7356,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>H 278-&gt;175 / C 148-&gt;148</t>
+          <t>H 278-&gt;255 / C 148-&gt;148</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
         <v>3.38</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
@@ -7406,7 +7406,7 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>H 203-&gt;163 / C 77-&gt;120</t>
+          <t>H 203-&gt;163 / C 45-&gt;91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>8.51</v>
+        <v>10.83</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8.16</v>
+        <v>3.72</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>430</v>
+        <v>302</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -7928,12 +7928,12 @@
       <c r="F4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>45</v>
+      <c r="G4" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>205-&gt;55 (air 35-&gt;50)</t>
+          <t>128-&gt;55 (air 35-&gt;50)</t>
         </is>
       </c>
     </row>

--- a/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ID 6.9 m (top/main) / 4.1 m (stripping) x 36.0 m T/T</t>
+          <t>ID 6.9 m (top/main) / 3.5 m (stripping) x 37.0 m T/T</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ID 2.6 m (top) / 6.6 m (main) / 3.0 m (boot) x 36.0 m T/T</t>
+          <t>ID 4.4 m (top) / 6.6 m (main) / 3.0 m (boot) x 36.0 m T/T</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60.7 MW abs. / 67.4 MW fired; 2-cell cabin, 8 passes, 128 rad. tubes 6" x 18.3 m</t>
+          <t>60.7 MW abs. / 67.4 MW fired; 2-cell cabin, 8 passes, 144 rad. tubes 6" x 18.3 m</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>545</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14.7 MW abs. / 16.7 MW fired; 1-cell cabin, 4 passes, 40 rad. tubes 6" x 18.3 m</t>
+          <t>14.7 MW abs. / 17.5 MW fired; 1-cell cabin, 4 passes, 44 rad. tubes 6" x 18.3 m</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1667 m2 bare; 2 bay(s) 6 m x 12 m, 4 fans</t>
+          <t>1667 m2 bare; 3 bay(s) 6 m x 12 m, 6 fans</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
         <v>33.75</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>881 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
+          <t>881 m2 bare; 2 bay(s) 6 m x 12 m, 4 fans</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
@@ -2785,13 +2785,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>403 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
+          <t>361 m2 bare; 1 bay(s) 6 m x 12 m, 2 fans</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>205-&gt;90 (air 35-&gt;85)</t>
+          <t>205-&gt;90 (air 35-&gt;60)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>398 m3/h rated @ 172 m</t>
+          <t>398 m3/h rated @ 244 m</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="n">
-        <v>250</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>CDU</t>
+          <t>VDU</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5434,10 +5434,10 @@
         <v>397.8</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>348.7436496087009</v>
@@ -5449,10 +5449,10 @@
         <v>0.7</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>188.9</v>
+        <v>267.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>OH2</t>
+          <t>API 674/675 PD</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -7859,13 +7859,13 @@
         <v>1667</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -8019,13 +8019,13 @@
         <v>881</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>6.64</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>403</v>
+        <v>361</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1</v>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>205-&gt;90 (air 35-&gt;85)</t>
+          <t>205-&gt;90 (air 35-&gt;60)</t>
         </is>
       </c>
     </row>

--- a/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-LST-001_Equipment-List.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>35 / 20</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>35 / 20</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>35 / 20</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>35 / 20</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>35 / 20</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>45 / 20</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>45 / 20</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>45 / 20</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>45 / 20</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>45 / 20</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30 / 20</t>
+          <t>45 / 20</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>37 m3/h rated @ 82 m</t>
+          <t>37 m3/h rated @ 144 m</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -4104,8 +4104,8 @@
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="3" t="n">
-        <v>18.5</v>
+      <c r="M68" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -4307,7 +4307,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>P-201A/B</t>
+          <t>P-119A/B</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4317,29 +4317,29 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product</t>
+          <t>Flare KO drum pump-out</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>VDU</t>
+          <t>CDU</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>198 m3/h rated @ 138 m</t>
+          <t>21 m3/h rated @ 76 m</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="n">
-        <v>110</v>
+      <c r="M73" s="3" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>P-202A/B</t>
+          <t>P-201A/B</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>HVGO pumparound / product</t>
+          <t>LVGO pumparound / product</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4376,36 +4376,36 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>391 m3/h rated @ 144 m</t>
+          <t>198 m3/h rated @ 138 m</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>A-8 (316)</t>
+          <t>S-6 (CS/12Cr)</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>P-203A/B</t>
+          <t>P-202A/B</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Slop wax</t>
+          <t>HVGO pumparound / product</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4425,19 +4425,19 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>12 m3/h rated @ 114 m</t>
+          <t>391 m3/h rated @ 144 m</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="3" t="n">
-        <v>5.5</v>
+      <c r="M75" s="2" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>P-204A/B</t>
+          <t>P-203A/B</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench)</t>
+          <t>Slop wax</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4474,19 +4474,19 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>196 m3/h rated @ 187 m</t>
+          <t>12 m3/h rated @ 114 m</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="n">
-        <v>132</v>
+      <c r="M76" s="3" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>P-205A/B</t>
+          <t>P-204A/B</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Hotwell sour water</t>
+          <t>Vacuum residue (incl. quench)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4523,36 +4523,36 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>13 m3/h rated @ 51 m</t>
+          <t>196 m3/h rated @ 187 m</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>395</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>S-6 (CS/12Cr)</t>
+          <t>A-8 (316)</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="3" t="n">
-        <v>3.7</v>
+      <c r="M77" s="2" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>P-206A/B</t>
+          <t>P-205A/B</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Hotwell slop oil</t>
+          <t>Hotwell sour water</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1 m3/h rated @ 60 m</t>
+          <t>13 m3/h rated @ 51 m</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4595,42 +4595,50 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="3" t="n">
-        <v>0.75</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>X-101</t>
+          <t>P-206A/B</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Demulsifier injection package</t>
+          <t>Hotwell slop oil</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CDU</t>
+          <t>VDU</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Tank 2 m3 + 2 x 100 % metering pumps</t>
+          <t>1 m3/h rated @ 60 m</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>SS316</t>
+          <t>S-6 (CS/12Cr)</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
@@ -4642,7 +4650,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>X-102</t>
+          <t>X-101</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4652,7 +4660,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Caustic injection package (desalted crude)</t>
+          <t>Demulsifier injection package</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4683,7 +4691,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>X-103</t>
+          <t>X-102</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4693,7 +4701,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Neutraliser / filming amine package (atm OH)</t>
+          <t>Caustic injection package (desalted crude)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4724,7 +4732,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>X-104</t>
+          <t>X-103</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4734,12 +4742,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Corrosion inhibitor package (VDU OH)</t>
+          <t>Neutraliser / filming amine package (atm OH)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>VDU</t>
+          <t>CDU</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4759,6 +4767,47 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>X-104</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion inhibitor package (VDU OH)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>VDU</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Tank 2 m3 + 2 x 100 % metering pumps</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>SS316</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="3" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -4773,7 +4822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5485,10 +5534,10 @@
         <v>36.8</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>50</v>
@@ -5500,10 +5549,10 @@
         <v>0.62</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>18.5</v>
+        <v>23.1</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -5728,41 +5777,41 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P-201A/B</t>
+          <t>P-119A/B</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LVGO pumparound / product</t>
+          <t>Flare KO drum pump-out</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>198.3</v>
+        <v>20.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>223.7069906480531</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>737</v>
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>800</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>110</v>
+        <v>5.7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>7.5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>BB2</t>
+          <t>OH2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5779,37 +5828,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P-202A/B</t>
+          <t>P-201A/B</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>HVGO pumparound / product</t>
+          <t>LVGO pumparound / product</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>391</v>
+        <v>198.3</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>314.9938703914651</v>
+        <v>223.7069906480531</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>709</v>
+        <v>737</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>154.8</v>
+        <v>81.3</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -5818,49 +5867,49 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>API 682 Plan 53B</t>
+          <t>API 682 Plan 11/52</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>A-8 (316)</t>
+          <t>S-6 (CS/12Cr)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>P-203A/B</t>
+          <t>P-202A/B</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Slop wax</t>
+          <t>HVGO pumparound / product</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>12.2</v>
+        <v>391</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>378.4357134139163</v>
+        <v>314.9938703914651</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>5.5</v>
+        <v>154.8</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>200</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -5881,37 +5930,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>P-204A/B</t>
+          <t>P-203A/B</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Vacuum residue (incl. quench)</t>
+          <t>Slop wax</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>195.6</v>
+        <v>12.2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>366.4357134139163</v>
+        <v>378.4357134139163</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>761</v>
+        <v>714</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>132</v>
+        <v>4.7</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -5932,70 +5981,70 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>P-205A/B</t>
+          <t>P-204A/B</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hotwell sour water</t>
+          <t>Vacuum residue (incl. quench)</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>13.5</v>
+        <v>195.6</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>51</v>
+        <v>187</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>990</v>
+        <v>14</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>366.4357134139163</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>761</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>3.7</v>
+        <v>112.3</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>132</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>OH2</t>
+          <t>BB2</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>API 682 Plan 11/52</t>
+          <t>API 682 Plan 53B</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>S-6 (CS/12Cr)</t>
+          <t>A-8 (316)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>P-206A/B</t>
+          <t>P-205A/B</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hotwell slop oil</t>
+          <t>Hotwell sour water</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.6</v>
+        <v>13.5</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>5</v>
@@ -6004,28 +6053,79 @@
         <v>45</v>
       </c>
       <c r="G24" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>OH2</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>API 682 Plan 11/52</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>S-6 (CS/12Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>P-206A/B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Hotwell slop oil</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H25" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I25" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J25" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>API 674/675 PD</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>API 682 Plan 11/52</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>S-6 (CS/12Cr)</t>
         </is>
@@ -6042,7 +6142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6610,6 +6710,132 @@
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Flare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PSV-1011</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>E-113 (steam side)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Blocked MP steam outlet (max. generation)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>8833</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1298</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1 x L</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Atmosphere (safe location)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PSV-2003</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>E-201 (steam side)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Blocked LP steam outlet (max. generation)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>3054</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>938</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1 x K</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Atmosphere (safe location)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TSV-typ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CW sides E-115, E-202..E-204</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Thermal expansion (blocked-in CW)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1 x D</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Grade</t>
         </is>
       </c>
     </row>
